--- a/data/trans_orig/P6906-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6906-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20794</t>
+          <t>21217</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>10688</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27050</t>
+          <t>26744</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58537</t>
+          <t>58114</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72603</t>
+          <t>72710</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20500</t>
+          <t>20714</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30207</t>
+          <t>30238</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84522</t>
+          <t>84828</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100965</t>
+          <t>100884</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>22338</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43347</t>
+          <t>42891</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15197</t>
+          <t>14851</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30474</t>
+          <t>30380</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54041</t>
+          <t>54400</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102634</t>
+          <t>103090</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>122838</t>
+          <t>123643</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37600</t>
+          <t>37946</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48531</t>
+          <t>48641</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144736</t>
+          <t>144377</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168303</t>
+          <t>168397</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,72%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13436</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30645</t>
+          <t>31774</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19038</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24881</t>
+          <t>25300</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48865</t>
+          <t>48429</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79299</t>
+          <t>78170</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96508</t>
+          <t>96551</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27495</t>
+          <t>26078</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39020</t>
+          <t>39007</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>107612</t>
+          <t>108048</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>131596</t>
+          <t>131177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30183</t>
+          <t>29052</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51317</t>
+          <t>49799</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13773</t>
+          <t>14067</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29641</t>
+          <t>30018</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48115</t>
+          <t>47172</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75226</t>
+          <t>74958</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85732</t>
+          <t>87250</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106866</t>
+          <t>107997</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58910</t>
+          <t>58533</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74778</t>
+          <t>74484</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150374</t>
+          <t>150642</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>177485</t>
+          <t>178428</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>79,09%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>88075</t>
+          <t>89686</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>126925</t>
+          <t>126337</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36699</t>
+          <t>36169</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60513</t>
+          <t>62153</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133854</t>
+          <t>132408</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>177728</t>
+          <t>178065</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>345380</t>
+          <t>345968</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>384230</t>
+          <t>382619</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>159608</t>
+          <t>157968</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>183422</t>
+          <t>183952</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>514699</t>
+          <t>514362</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>558573</t>
+          <t>560019</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,88%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2012 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20983</t>
+          <t>21419</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17375</t>
+          <t>17829</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17471</t>
+          <t>18163</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33801</t>
+          <t>34453</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55597</t>
+          <t>55161</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68545</t>
+          <t>68401</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16887</t>
+          <t>16433</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27920</t>
+          <t>28057</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77041</t>
+          <t>76389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93371</t>
+          <t>92679</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14749</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32887</t>
+          <t>31844</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14191</t>
+          <t>14054</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30912</t>
+          <t>30592</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32818</t>
+          <t>33448</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56593</t>
+          <t>56127</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58919</t>
+          <t>59962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77046</t>
+          <t>77057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32586</t>
+          <t>32906</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49307</t>
+          <t>49444</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98711</t>
+          <t>99177</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>122486</t>
+          <t>121856</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19886</t>
+          <t>20120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38729</t>
+          <t>37590</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17679</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28627</t>
+          <t>29939</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51698</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40828</t>
+          <t>41967</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59671</t>
+          <t>59437</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35300</t>
+          <t>34473</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47145</t>
+          <t>46769</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80838</t>
+          <t>80530</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>103909</t>
+          <t>102597</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>77,41%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12158</t>
+          <t>12310</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27142</t>
+          <t>28304</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12727</t>
+          <t>12661</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27834</t>
+          <t>27615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29037</t>
+          <t>29036</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49658</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51139</t>
+          <t>49977</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66123</t>
+          <t>65971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36262</t>
+          <t>36481</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51369</t>
+          <t>51435</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92789</t>
+          <t>92720</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>113341</t>
+          <t>113342</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68102</t>
+          <t>69182</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101429</t>
+          <t>100999</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50884</t>
+          <t>50686</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77900</t>
+          <t>78378</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>127966</t>
+          <t>128695</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169978</t>
+          <t>172629</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>224796</t>
+          <t>225226</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>258123</t>
+          <t>257043</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136935</t>
+          <t>136457</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>163951</t>
+          <t>164149</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>371082</t>
+          <t>368431</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>413094</t>
+          <t>412365</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,21%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20766</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14748</t>
+          <t>14631</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13522</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29950</t>
+          <t>30859</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33907</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47638</t>
+          <t>47953</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15167</t>
+          <t>15284</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>25330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54638</t>
+          <t>53729</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71066</t>
+          <t>70099</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>82,87%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9051</t>
+          <t>9399</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27243</t>
+          <t>26502</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26957</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25721</t>
+          <t>25066</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49472</t>
+          <t>47522</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69741</t>
+          <t>70482</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87933</t>
+          <t>87585</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28595</t>
+          <t>28686</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43495</t>
+          <t>42956</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103063</t>
+          <t>105013</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126814</t>
+          <t>127469</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,57%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20091</t>
+          <t>19959</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39438</t>
+          <t>39476</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11280</t>
+          <t>11264</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24858</t>
+          <t>25949</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35050</t>
+          <t>34975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60175</t>
+          <t>58092</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70497</t>
+          <t>70459</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89844</t>
+          <t>89976</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39889</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53467</t>
+          <t>53483</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>114507</t>
+          <t>116590</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139632</t>
+          <t>139707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18029</t>
+          <t>17920</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36221</t>
+          <t>35106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34257</t>
+          <t>33334</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40001</t>
+          <t>39472</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63689</t>
+          <t>63696</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,23%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52189</t>
+          <t>53304</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70381</t>
+          <t>70490</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>32749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48535</t>
+          <t>49615</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90804</t>
+          <t>90797</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>114492</t>
+          <t>115021</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,45%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67365</t>
+          <t>66641</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101921</t>
+          <t>100637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57639</t>
+          <t>55820</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85697</t>
+          <t>83491</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>134773</t>
+          <t>132743</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>177346</t>
+          <t>177122</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>248080</t>
+          <t>249364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>282636</t>
+          <t>283360</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130601</t>
+          <t>132807</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>158659</t>
+          <t>160478</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>388953</t>
+          <t>389177</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>431526</t>
+          <t>433556</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,56%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23293</t>
+          <t>24457</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8925</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18581</t>
+          <t>17870</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17838</t>
+          <t>17699</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36531</t>
+          <t>37749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47922</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64199</t>
+          <t>64355</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36100</t>
+          <t>36811</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45756</t>
+          <t>46511</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89366</t>
+          <t>88148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>108059</t>
+          <t>108198</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,94%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12132</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30671</t>
+          <t>30126</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19218</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34150</t>
+          <t>33984</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34570</t>
+          <t>33962</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58795</t>
+          <t>57501</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81312</t>
+          <t>81857</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99851</t>
+          <t>100339</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64580</t>
+          <t>64746</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79512</t>
+          <t>79723</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>151917</t>
+          <t>153211</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176142</t>
+          <t>176750</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,88%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16734</t>
+          <t>16708</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31259</t>
+          <t>31092</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12256</t>
+          <t>12019</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39842</t>
+          <t>40259</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38543</t>
+          <t>38569</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50773</t>
+          <t>50674</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65649</t>
+          <t>65816</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90222</t>
+          <t>91070</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112342</t>
+          <t>111925</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139928</t>
+          <t>140165</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15018</t>
+          <t>14643</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33153</t>
+          <t>32878</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23964</t>
+          <t>23887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41232</t>
+          <t>41077</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42980</t>
+          <t>43022</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66844</t>
+          <t>67758</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67877</t>
+          <t>68152</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86012</t>
+          <t>86387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62664</t>
+          <t>62819</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79932</t>
+          <t>80009</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>138082</t>
+          <t>137168</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>161946</t>
+          <t>161904</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50125</t>
+          <t>49279</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82915</t>
+          <t>82439</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64394</t>
+          <t>63793</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106237</t>
+          <t>106128</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>127376</t>
+          <t>128239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>181106</t>
+          <t>177729</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>256590</t>
+          <t>257066</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>289380</t>
+          <t>290226</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>247978</t>
+          <t>248087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>289821</t>
+          <t>290422</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>512614</t>
+          <t>515991</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>566344</t>
+          <t>565481</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
